--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.4  |  11 controls</t>
+          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.4  |  12 controls</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Current license inventory has been documented including base licenses and compliance/security add-ons; License gap analysis has been completed comparing current state to governance requirements per control; Prerequisite base license requirements for Copilot are confirmed met for target user populations, including Frontline (F1/F3) user populations where applicable; Governance add-on license requirements are identified and procurement plan is in place; Phased rollout plan is documented with specific user populations, dates, and governance prerequisites per phase; Frontline user populations are explicitly included or excluded with documented rationale; License assignment uses group-based licensing (security groups) rather than individual assignment; Governance readiness gating criteria are defined for each phase (Recommended and Regulated levels); License usage monitoring is configured with 90-day review cadence (Recommended and Regulated levels); If PAYG Copilot Chat is in use: the billing policy is connected to the approved service, covered users or groups are documented, budget notifications are configured, and monthly cost review evidence is retained; License strategy has been reviewed and approved by appropriate stakeholders (IT, finance, compliance); License governance documentation is maintained and accessible for regulatory examination (Regulated level), including coverage for Frontline and PAYG billing models</t>
+          <t>License assignment strategy document with role/risk-tier mapping; Current license utilization report from M365 admin center; License reclamation cadence and recent reclamation evidence; PAYG budget thresholds and alert configuration</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Executive sponsor has been identified and is actively engaged in Copilot deployment oversight; Stakeholder communication plan has been developed and is being executed per deployment phase; User FAQ document or guide has been created and distributed to target user populations; Champion network has been established with representatives across deployment departments (Recommended and Regulated levels); User readiness assessment process is defined and being applied before license assignment (Recommended and Regulated levels); Adoption metrics are being tracked and reviewed at established cadence (weekly during rollout, monthly ongoing); Resistance management strategies have been identified and are being applied as needed; Steering committee is meeting at established cadence and reviewing adoption progress (Recommended and Regulated levels); Board-level awareness of Copilot deployment has been established (Regulated level); Change management documentation is maintained and accessible for regulatory examination (Regulated level)</t>
+          <t>Change-management and adoption plan document; Executive sponsor designation and communication cadence; Success metrics / KPIs for Copilot adoption; Stakeholder communication log or newsletter archive</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Foundation training module has been developed covering Copilot basics, responsible AI, and data sensitivity; Training is required before Copilot license assignment at the appropriate level per governance tier; Training completion rates are tracked and reported by department and role; Regulatory Awareness module has been developed covering FSI-specific requirements (Recommended and Regulated levels); Role-specific training modules have been developed for at least client-facing, compliance, and admin roles (Recommended and Regulated levels); Knowledge assessments are included with defined passing scores (Recommended and Regulated levels); Annual refresher training cadence is established with expiration and renewal process; Hands-on workshops have been conducted for each deployment phase (Recommended and Regulated levels); Training records are maintained in a format suitable for regulatory examination (Regulated level); Training program effectiveness is reviewed annually with documented findings and improvements (Regulated level)</t>
+          <t>Training completion report with percentage of in-scope users trained; Acceptable-use policy and acknowledgement tracking records; Training curriculum covering responsible AI use and firm policies; Annual refresh date for training content</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Run `Get-CsTeamsMeetingPolicy -Identity "FSI-Regulated-Policy" — Select-Object CopilotWithoutTranscript`; Review Teams meeting policies in Teams Admin Center — Copilot enablement aligns with documented governance decisions; no policy uses the `Enabled` (without transcript) setting for regulated groups; Verify retention policies cover meeting transcripts and recap content — Retention policies applied to Exchange Online and OneDrive locations; Test Copilot behavior in a meeting with a restrictive sensitivity label — Copilot is blocked or limited per label configuration; Confirm participant notification appears when Copilot is active — All meeting participants see Copilot notification banner; Search eDiscovery for Copilot meeting artifacts — Recap content, transcripts, and notes are discoverable; Review supervisory review queue for meeting summaries (Regulated) — Meeting summaries appear in the communication compliance review queue; Verify opt-out capability for meeting organizers — Organizer can disable Copilot before and during a meeting; Confirm immutable storage for meeting records (Regulated) — WORM-compliant storage configured for applicable records</t>
+          <t>Teams meeting policy configuration showing Copilot settings; Meeting organizer control documentation; Transcription retention policy aligned to regulatory requirements; Governance policy document for Copilot in meetings</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Review Teams calling policies for Copilot settings — Copilot enabled only for approved user groups; Verify call recording consent notifications — Notifications active and compliant with applicable jurisdictions; Confirm retention policies cover all call content types — Recordings, transcripts, summaries, and voicemails under retention; Test information barriers in Queues agent assist — Restricted content is not surfaced to barriered agents; Search eDiscovery for Copilot call summaries — Call summaries are discoverable and searchable; Review supervisory review queue for call summaries (Regulated) — Flagged call summaries appear in review queue within SLA; Verify accuracy sampling results from most recent quarter — Sampling completed and documented with findings; Confirm compliance recording integration captures Copilot artifacts — Third-party recording platform captures or references Copilot content</t>
+          <t>Teams calling policy configuration for Copilot features; Call-recording retention policy aligned to regulatory minimum; Governance document covering call summarization and analytics; Queue configuration with Copilot feature settings</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Review Viva Insights aggregation minimum settings — Minimum set to 25 or higher for regulated departments; Verify employee opt-out process is documented and communicated — Opt-out instructions published and accessible; Confirm excluded groups in Viva Insights admin settings — Legal, compliance, HR, internal audit excluded from org analytics; Confirm Copilot Chat usage reporting is active in Viva Insights — Copilot Chat adoption and usage metrics visible at department level; Review Viva Engage retention policies — Retention policies applied to Viva Engage content; Verify Engage-to-Teams integration compliance coverage — Teams Communication Compliance policies confirmed to capture surfaced Engage content; Verify Viva Learning is not sole tracking system for regulatory training — Official CE/FE systems remain system of record; Confirm Viva Pulse anonymity settings — Minimum response threshold enforced; anonymity maintained; Review HR attribute configuration in Viva Insights — Only approved attributes available for analysis; Confirm annual privacy impact assessment (Regulated) — Assessment completed within past 12 months</t>
+          <t>Viva Copilot governance policy document; Privacy control configuration for Viva Insights; Approved user group scoping for Copilot features; Governance review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Access Copilot usage reports — Reports are accessible and populated; Review latest monthly usage summary — Summary exists and is current; Verify report access roles — Only designated personnel have access; Confirm segmentation is available or documented — Department/risk-based reporting exists; Review anomaly thresholds — Thresholds are defined and used; Confirm governance committee reporting — Periodic reporting is delivered to the intended audience; Review agent metrics if agents are enabled — Agent Overview data is incorporated into operational reporting; Confirm archival of reports — Governance reports are retained per policy</t>
+          <t>Copilot usage report from Microsoft 365 admin center; Leadership reporting cadence and most recent report; Anomaly detection configuration and recent alerts; ROI/adoption metric dashboard or report</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Review feedback settings in M365 Admin Center — Screenshots disabled, Microsoft contact disabled; Verify diagnostic data level configuration — Set to "Required" (not "Optional"); Confirm connected experiences settings — Non-essential connected experiences disabled; Review data flow documentation — Documented and current within past 12 months; Verify employee communication was distributed — Communication sent and acknowledged; Review privacy impact assessment coverage — Copilot feedback/telemetry included in PIA; Confirm DPA coverage of Copilot data — Microsoft DPA reviewed and coverage confirmed; Verify configuration change audit trail (Regulated) — Changes to feedback/telemetry settings are logged</t>
+          <t>Feedback review cadence and routing documentation; Privacy controls for feedback/telemetry data handling; Product owner assignment for feedback triage; Most recent feedback review summary</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Review license inventory in M365 Admin Center — Inventory current and reconciled to vendor billing, including PAYG user groups; Verify department-level cost allocation reports — Reports produced monthly with accurate department mapping for both per-seat and PAYG costs; Confirm license reclamation process is operational — Inactive users identified and reclamation workflow functioning; Verify PAYG budgets and notifications are configured (if PAYG enabled) — Active billing policies have budgets and notification routing configured; Review ROI tracking documentation — ROI analysis updated quarterly with actual metrics and documented per-seat versus PAYG population decisions; Verify group-based license assignment — Licenses assigned via Entra ID groups, not individual assignment; Confirm budget forecast includes Copilot costs — Current fiscal year budget includes both per-seat licensing and PAYG estimated cost line items; Review license utilization report — Report shows assigned vs. active usage with optimization recommendations; Verify PAYG cost anomaly monitoring — Cost Management review evidence exists and unusual usage is investigated; Verify audit trail for license changes — Assignment, reclamation, billing-policy changes, and PAYG enablement events are logged and retrievable</t>
+          <t>Cost allocation report by business unit / cost center; License reclamation cadence and recent reclamation records; PAYG cost tracking dashboard with budget alerts; Chargeback/showback documentation</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -988,20 +988,59 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Review Message Center monitoring configuration — Notifications configured and distributed to governance team; Verify targeted release ring configuration — Pilot group defined with appropriate membership; Review change register for completeness — All Copilot-related MC posts tracked with governance decisions; Confirm impact assessments are completed for Medium+ changes — Assessments documented with approvals; Verify pilot testing documentation for recent feature changes — Testing results available for features in targeted release; Review CAB or governance meeting minutes for Copilot changes — Copilot changes discussed and documented in governance forums; Confirm post-implementation reviews are completed — PIRs done within 30 days of significant feature deployments; Verify change management evidence package (Regulated) — Documentation sufficient for SOX ITGC audit review</t>
+          <t>Change advisory board records for Copilot feature rollouts; M365 Message Center monitoring evidence; Risk review documentation for recent feature changes; Approval records for tenant-managed feature enablement</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
     </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Copilot Cowork Governance</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft 365 Copilot Cowork (Frontier preview) governed with deliberate availability, plugin, and supervision decisions before broad enablement?</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Frontier preview enrollment record for tenant and admin accounts; Cowork availability configuration (scoped group or blocked) with approval; Approved Cowork plugin inventory and connector authentication records; Deployment/pinning approvals and supervision/audit coverage evidence</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I15"/>
+  <autoFilter ref="A4:I16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.4  |  12 controls</t>
+          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8  |  13 controls</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Is Microsoft 365 Copilot Cowork (Frontier preview) governed with deliberate availability, plugin, and supervision decisions before broad enablement?</t>
+          <t>Is Microsoft 365 Copilot Cowork governed at GA with deliberate billing/discovery, model/browser, plugin/skill, and supervision decisions before broad enablement?</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1033,14 +1033,53 @@
       <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="7" t="inlineStr"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I16"/>
+  <autoFilter ref="A4:I17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8  |  13 controls</t>
+          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8.0  |  13 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Frontier preview enrollment record for tenant and admin accounts; Cowork availability configuration (scoped group or blocked) with approval; Approved Cowork plugin inventory and connector authentication records; Deployment/pinning approvals and supervision/audit coverage evidence</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.4  |  12 controls</t>
+          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8.0  |  13 controls</t>
         </is>
       </c>
     </row>
@@ -1022,25 +1022,64 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Is Microsoft 365 Copilot Cowork (Frontier preview) governed with deliberate availability, plugin, and supervision decisions before broad enablement?</t>
+          <t>Is Microsoft 365 Copilot Cowork governed at GA with deliberate billing/discovery, model/browser, plugin/skill, and supervision decisions before broad enablement?</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Frontier preview enrollment record for tenant and admin accounts; Cowork availability configuration (scoped group or blocked) with approval; Approved Cowork plugin inventory and connector authentication records; Deployment/pinning approvals and supervision/audit coverage evidence</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="7" t="inlineStr"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I16"/>
+  <autoFilter ref="A4:I17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Copilot usage report from Microsoft 365 admin center; Leadership reporting cadence and most recent report; Anomaly detection configuration and recent alerts; ROI/adoption metric dashboard or report</t>
+          <t>Successful Microsoft Graph beta usage-detail export artifact (JSON or CSV) with timestamp and period; At least one usage-detail record returned for the selected period (fail closed if empty); Permission evidence for Reports.Read.All and supported delegated role or app consent; Documented caveats for beta API behavior, national-cloud availability (global only), and unlicensed Copilot Chat data exclusion</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>License Planning and Copilot Assignment Strategy</t>
+          <t>Is Copilot license assignment reconciled against approved entitlement and eligibility criteria on a documented cadence?</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Copilot Admin Settings and Feature Management</t>
+          <t>Are Microsoft 365 Copilot admin settings reviewed and configured per the organization's governance policy on a documented cadence?</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Copilot in Teams Meetings Governance</t>
+          <t>Are Teams meeting policies governing Copilot in meetings, including transcription prerequisites, reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Copilot in Teams Phone and Queues Governance</t>
+          <t>Are Teams calling and voice-application policies that expose Copilot features reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
